--- a/Topic Relevant Comments/Kenya/Andrew Kibe_I Wonder How Some Men Are Satisfied.xlsx
+++ b/Topic Relevant Comments/Kenya/Andrew Kibe_I Wonder How Some Men Are Satisfied.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>text</t>
   </si>
@@ -25,96 +25,33 @@
     <t>Studies in shared cultures show monogamous marriages tend to be more stable: lower divorce rates overall, with polygynous ones (esp. 3+ wives) up to 5x higher. Women in polygamous setups face 2.25x higher depression odds and worse family functioning/satisfaction per 2021 meta-analysis. Husbands often report higher satisfaction with extra wives. Recent data finds no clear child outcome edge for monogamy, sometimes polygyny aids resilience in tough conditions. Success hinges on culture and people.</t>
   </si>
   <si>
-    <t>What a man thinken is what he becomes,real mean are out here chasing real dreams not entertaining how many women he should have or cars, because his all efforts is on how to produce solutions to daily life challenges 💯💪</t>
-  </si>
-  <si>
-    <t>It's called self respect, some men don't want their bodies to be seen by everyone, mind you once a woman sleeps with a man the respect is thrown away, instead of saying Mr so,she will call by your first name</t>
-  </si>
-  <si>
     <t>True love isn't about variety, it's about loyalty. A man who truly loves invests in one heart... that's passion, not brokenness 💯</t>
   </si>
   <si>
     <t>If you really think having several women makes you a man, you already lost. As a man, have something going on in your life other than just focusing on women...</t>
   </si>
   <si>
-    <t>Kibe his right ....u can't protect something thats it's not yours .many men in Kenya does not love themselves. Wake up ur not his father</t>
-  </si>
-  <si>
     <t>They are not 🌹 Majority are CONDITIONED by religion and PROGRAMMED by society 🌹 Some lack the financial capacity &amp; Status 🌹 Men PRETEND most to enjoy Marriage Lastly, majority of us MEN Are TOLERANCE as SIZE of our Pocket &amp; LEVEL of our accomplishment</t>
   </si>
   <si>
-    <t>Agreed. Even the men in the Bible had one mission, to serve their higher purpose. Abraham, Issac, Jacob had 3+ wives. That's how they multiplied faster. Modern man is serving a woman, giving power to the wrong purpose. I'l be marrying 3 wives , several hot side chicks too</t>
-  </si>
-  <si>
     <t>capitalism dicapasitated our cognition and abandoned our nation-ship (Culture), hashish, traditionally monogamy was seen as deficiency and polygamy was wealth. you are right on the brokeness part, sickness maybe the christians</t>
   </si>
   <si>
-    <t>Monogamy is often just a fancy word for "lack of options." If you have the drive to own the fleet, the estate, and the empire, why would you stop at the shoreline of your personal life? Top G's don't settle for "just one" of anything. G's lead circles not lines.</t>
-  </si>
-  <si>
-    <t>Things I want to hear in men's circles. A man should keep several women. And every week you are on a business trip.</t>
-  </si>
-  <si>
     <t>By pooling emotional and financial capital with one high-value woman, a man creates a "Synergistic Compound" that accelerates wealth creation. A car is a tool you drive; a wife is a partner you build with.</t>
   </si>
   <si>
-    <t>My grandfather had multiple wives 😂 There is sense in your statement Kifee...every living thing male tend to accommodate multiple wives so you are right 👍</t>
-  </si>
-  <si>
     <t>Same way am satisfied being Kenyan I will still be satisfied being a one woman man. Real Men other important things to do other than running from one Bermuda triangle to another.</t>
   </si>
   <si>
-    <t>Ow several.and settle witg 9 wives</t>
-  </si>
-  <si>
-    <t>You are the one who is sick. What do multiple women add a man?</t>
-  </si>
-  <si>
-    <t>We exist. Those with only one Woman.</t>
-  </si>
-  <si>
     <t>Napenda hao wanaume wanajua what true love is they are talking with dignity</t>
   </si>
   <si>
-    <t>It's weakness and oneitis</t>
-  </si>
-  <si>
-    <t>In nature's software a man was given the power to impregnate at infinity(poly)...I mean he can impregnate at any point but Women conceive a seed at a time(mono)</t>
-  </si>
-  <si>
-    <t>Could you show us that ONE woman you have LOVED? or TWO? There is a huge difference between loving a woman and having sex with a woman</t>
-  </si>
-  <si>
-    <t>One man lost, we are down one man, less one. The statement is psychologically crippled</t>
-  </si>
-  <si>
-    <t>msee kitu huwa unafikiria tu ni kukula women 😂 🫴 hakunanga kitu ingine,</t>
-  </si>
-  <si>
     <t>U just need one good woman in ur life ,and u will see the Greatness of that love . I personally think that a man who finds satisfaction in one woman is greater than a man who finds love in several . No offence ima big fan</t>
   </si>
   <si>
-    <t>You're misleading men into having an abundance mindset, You're a bad guy men.</t>
-  </si>
-  <si>
-    <t>Discipline bois, learn to be disciplined. Get your 4 women and settle.</t>
-  </si>
-  <si>
-    <t>And that's the reason you are still roaming in the city as a single man without responsibility of being Aman in your own home at 58?</t>
-  </si>
-  <si>
     <t>Some people are just happy with one. The guy who gets his dream car (girl) will cherish it with everything he has. He will polish it and make sure everything is perfect all the time. The rich (spoiled) guy that has multiple (whatever) has to divide his attention between them all. Not one is special to him. He doesn't have the time to focus on one because he has so many. When you can't full devote all your undivided attention something's will definitely fall through the cracks.</t>
   </si>
   <si>
-    <t>😂😂😂,huyu heartbreak inaeza muua aki.</t>
-  </si>
-  <si>
-    <t>Nimeambia ivi msee mwenye analea mtoto si wake amenitusi vibaya</t>
-  </si>
-  <si>
-    <t>you loosing it now gathee. same bitches we are avoiding ?</t>
-  </si>
-  <si>
     <t>how successful are monogamous marriages compared to polygamous ones?</t>
   </si>
   <si>
@@ -124,63 +61,27 @@
     <t>Most women are unimpressive compared to men but when two people who have worked on themselves come together they have no choice but to be consumed in one another. It's not just men that 'settle' your Russian egonga alipita na married women because they settled.</t>
   </si>
   <si>
-    <t>makosaa unafanya is putting women and cars on the same sentence</t>
-  </si>
-  <si>
-    <t>Women are human beings with feelings, not cars to be owned by men.Gosh, women need to normalise hating men!Women you are better off alone with your cats than with stupid men like this!Tujipende please!</t>
-  </si>
-  <si>
     <t>Some men have other things to think about other than their dicks. Some men just value themselves enough to know that they can also love themselves more than cars. Some men just value themselves like that.</t>
   </si>
   <si>
     <t>People aren't cars. Some men value depth over variety. Loyalty isn't brokenness; it's a choice.</t>
   </si>
   <si>
-    <t>So NI gari ama NI women</t>
-  </si>
-  <si>
     <t>Exclusive partnership,availability and reciprocity is common in such setups. I endorse them 💯</t>
   </si>
   <si>
-    <t>Brokeness and kukosa nguvu za kiume</t>
-  </si>
-  <si>
-    <t>Love for women has led many men to graves and poverty.</t>
-  </si>
-  <si>
-    <t>This ain't about women</t>
-  </si>
-  <si>
-    <t>Brokenness na kujiheshimu pia</t>
-  </si>
-  <si>
-    <t>Everything is spiritual. Some men jaut dont want to deal with the many spirits from different women.</t>
-  </si>
-  <si>
     <t>Brokenness? Sickness? Nah. Some men just have options and the capacity to handle them. If you love cars, you don't park one in the garage for life and act like the showroom doesn't exist. You appreciate variety, performance, different drives. The problem isn't wanting more it's lying about it. If you're built for one, cool. If you're built for a fleet, own it.</t>
   </si>
   <si>
-    <t>Mens becareful of whom you sleep with ! Sex is spiritual. It can make you or break you! So as much as is your king of advice..this one ☝️ today i disagree with.</t>
-  </si>
-  <si>
     <t>Women are not cars so your line of reasoning is already questionable. Lakini anto daher adek tatu.</t>
   </si>
   <si>
-    <t>Where is the lie, siku wanawake wana nunuliwa. They go with the highest bidder!</t>
-  </si>
-  <si>
-    <t>Na hii akili ndo mnataka kuleta change nayo kama kazi ni wanawake na pombe.</t>
-  </si>
-  <si>
     <t>Women are not cars</t>
   </si>
   <si>
     <t>Treating hearts like a car collection is a bold strategy, but most men just can't afford the "maintenance" costs of multiple models. One engine is usually enough to keep life running!</t>
   </si>
   <si>
-    <t>Men who follow Kifee are lambistic and puny just like him</t>
-  </si>
-  <si>
     <t>So you can have a favourite parent, child, cousin, auntie, uncle, niece &amp; nephew but cars and women is where you draw the line ...you must have 1 to cherish it...I wanda 🚮</t>
   </si>
   <si>
@@ -190,112 +91,16 @@
     <t>Reasons why a Woman cannot be compared to material things like a car..?</t>
   </si>
   <si>
-    <t>Cars are more important than women anyday and everyday, women like you should be compared to the lowest comparison of the grid</t>
-  </si>
-  <si>
-    <t>It's not comparing women to cars it's completely women to some expensive shiet?</t>
-  </si>
-  <si>
-    <t>Women should be compared to cows nevertheless</t>
-  </si>
-  <si>
-    <t>Women are not cars. Thats the easiest way to end up broke, dead or in deep s@*t.</t>
-  </si>
-  <si>
-    <t>Men are not motorcycles with one headlamp. Diversify, seduce fuck more women.</t>
-  </si>
-  <si>
-    <t>Because cars don't grow on trees Kibe Each woman comes with a bill</t>
-  </si>
-  <si>
-    <t>Sisi tuna address serious issues kwa economy wewe bado uko kwa kinywero</t>
-  </si>
-  <si>
-    <t>Some people don't even choose women bana</t>
-  </si>
-  <si>
     <t>You're just casually comparing women with cars. The hate is deep rooted.</t>
   </si>
   <si>
     <t>This has nothing to do with love</t>
   </si>
   <si>
-    <t>People like kibe are damaged beyond repair. So they're coming to influence weak minds here. Misery loves company.</t>
-  </si>
-  <si>
-    <t>Women are not cars you dumb toad!</t>
-  </si>
-  <si>
-    <t>Not everyone is immoral like you</t>
-  </si>
-  <si>
     <t>I know what you're saying but cars are not people with their own personality and so on. If women didn't have that it would be lame. If you can figure out how to be openly with more than one, it's possible and much more fulfilling than just buying another thing.</t>
   </si>
   <si>
-    <t>For satisfaction and internal ,only one loveable girl is enough because our soul except only one as his mate other are extra rush in mind</t>
-  </si>
-  <si>
-    <t>Health wise broh ,sio kupita na kila mtu,apart from echaivi kuna herpes ,sio eti nini bit soko ndio chafu</t>
-  </si>
-  <si>
-    <t>Hiyo mindset Yako ni expensive Mzee. Do not ever lose your focus because of some few inches of body part, I mean we have other great body parts too like the brain, the nose and Many others</t>
-  </si>
-  <si>
-    <t>So you should be equated to dowry cows?</t>
-  </si>
-  <si>
-    <t>Mmoja amenishinda already,, I like solitude due to lack of funds</t>
-  </si>
-  <si>
-    <t>Satisfaction is the same.</t>
-  </si>
-  <si>
-    <t>Kwani gari unachukua for free?</t>
-  </si>
-  <si>
-    <t>Yeah until your fun days are over, age reduces your movement to atound house and you're not fun 😒 anymore. You be sitting alone and hating the living coz you be dead waiting for your death day. Angel of death is patient with this type. It is fucked up if you are broke.</t>
-  </si>
-  <si>
-    <t>It's free will my friend you can choose what you want and it's perfectly okay.</t>
-  </si>
-  <si>
-    <t>Wewe ni fala. Endelea kumislead watu simply because it didn't work out how you wanted it. Everyone ain't same</t>
-  </si>
-  <si>
-    <t>Brokeness it is.</t>
-  </si>
-  <si>
     <t>A woman is like a tea bag you never know how strong she is until she gets in hot water</t>
-  </si>
-  <si>
-    <t>Exactly, I was thinking the same 🙄🙄</t>
-  </si>
-  <si>
-    <t>When my brokenness is cured, this sickness will disappear instantly. Nawa pile kwa tray kama mayai. Gaddamit.</t>
-  </si>
-  <si>
-    <t>You will cry one day</t>
-  </si>
-  <si>
-    <t>Cars don't have STIs and some funny spiritual baggage.</t>
-  </si>
-  <si>
-    <t>Solomo wanst punished by God bytheway. So your point is invalid</t>
-  </si>
-  <si>
-    <t>Kumbe the more I repeat reading the more am getting confused🤔</t>
-  </si>
-  <si>
-    <t>I keep asking the same question</t>
-  </si>
-  <si>
-    <t>It's principle and you have NONE .</t>
-  </si>
-  <si>
-    <t>They are too much work</t>
-  </si>
-  <si>
-    <t>I can't afford all the repairs plus insurance...</t>
   </si>
 </sst>
 </file>
@@ -653,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A94"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -801,331 +606,6 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1">
-      <c r="A87" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1">
-      <c r="A89" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1">
-      <c r="A91" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1">
-      <c r="A93" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94" t="s">
-        <v>93</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
